--- a/projects/QNL/QNL_datapoint_ledger_v2.xlsx
+++ b/projects/QNL/QNL_datapoint_ledger_v2.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,6 @@
           <t>QNL datapoint ledger v2</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,12 +514,8 @@
           <t>Rebuilt from the reviewer decisions in column AF ("My suggestions") and validated against QF_SSC_Ontology_ver02.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -617,10 +612,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
@@ -702,6 +694,62 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>Genuinely new para class to hand over: para:Trip_Alarm (subclass brick:Alarm, following SSC Fail_*_Alarm pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Build status (updated)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>All signatures placed</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Per-unit membership now comes from Selected_PARA_OS_Data_Points_v4.0.xlsx, so both universal and partial-coverage signatures are written. 2,215 points on AHU/VAV/CAV/FCU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Timeseries ids</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Filled from the IO list SourceTag - no placeholders remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Taken from the IO list, not the Selected sheet: 30 Selected rows have humidity/temperature units transposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AHU, VAV, CAV, FCU only. CCU/EF/DX/HEX/KEF/SEF/TEF/GEN are out of scope - no equipment in the register.</t>
         </is>
       </c>
     </row>
